--- a/data/predictions/Roohan.xlsx
+++ b/data/predictions/Roohan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/World Cup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb8ff3dc0463a38e/Documents/Personal Projects/World Cup/data/predictions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{857C9C5B-B58E-437E-92A4-01653F9861F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FDBAC4D-0744-43AD-9E89-37D66250E6F5}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{857C9C5B-B58E-437E-92A4-01653F9861F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85B29D5A-DB37-4F7C-B266-7322AF95FBE5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roohan" sheetId="1" r:id="rId1"/>
@@ -319,6 +319,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
